--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,19 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.79184</v>
+        <v>16.92946</v>
       </c>
       <c r="D2" t="n">
-        <v>16.96321</v>
+        <v>16.66223</v>
       </c>
       <c r="E2" t="n">
-        <v>16.55234</v>
+        <v>16.92454</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.01643</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05178</v>
+        <v>0.05147</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81623</v>
+        <v>1.84242</v>
       </c>
     </row>
     <row r="3">
@@ -482,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.99245</v>
+        <v>17.36961</v>
       </c>
       <c r="D3" t="n">
-        <v>16.7747</v>
+        <v>16.50626</v>
       </c>
       <c r="E3" t="n">
-        <v>16.80317</v>
+        <v>16.6712</v>
       </c>
       <c r="F3" t="n">
-        <v>43.24796</v>
+        <v>43.16881</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.05042</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85058</v>
+        <v>1.81327</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +509,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="C4" t="n">
+        <v>16.90556</v>
       </c>
       <c r="D4" t="n">
-        <v>16.60829</v>
+        <v>16.72711</v>
       </c>
       <c r="E4" t="n">
-        <v>16.88229</v>
+        <v>16.83404</v>
       </c>
       <c r="F4" t="n">
-        <v>42.70772</v>
+        <v>42.3093</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05019</v>
+        <v>0.05077</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85215</v>
+        <v>1.84724</v>
       </c>
     </row>
     <row r="5">
@@ -533,25 +534,23 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>16.96321</v>
       </c>
       <c r="D5" t="n">
-        <v>16.6985</v>
+        <v>16.55234</v>
       </c>
       <c r="E5" t="n">
-        <v>17.13106</v>
+        <v>16.79184</v>
       </c>
       <c r="F5" t="n">
-        <v>43.45165</v>
+        <v>42.15219</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0502</v>
+        <v>0.05178</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81353</v>
+        <v>1.81623</v>
       </c>
     </row>
     <row r="6">
@@ -561,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.83221</v>
+        <v>16.99245</v>
       </c>
       <c r="D6" t="n">
-        <v>16.58779</v>
+        <v>16.7747</v>
       </c>
       <c r="E6" t="n">
-        <v>16.83131</v>
+        <v>16.80317</v>
       </c>
       <c r="F6" t="n">
-        <v>42.07722</v>
+        <v>43.24796</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05075</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#DIV/0!</v>
+        <v>0.05177</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.85058</v>
       </c>
     </row>
     <row r="7">
@@ -586,24 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.97388</v>
+        <v>17.00667</v>
       </c>
       <c r="D7" t="n">
-        <v>16.77606</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 16.48 </t>
-        </is>
+        <v>16.60829</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.88229</v>
       </c>
       <c r="F7" t="n">
-        <v>43.19623</v>
+        <v>42.70772</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05086</v>
+        <v>0.05019</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89086</v>
+        <v>1.85215</v>
       </c>
     </row>
     <row r="8">
@@ -613,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.83086</v>
+        <v>17.13106</v>
       </c>
       <c r="D8" t="n">
-        <v>16.49846</v>
+        <v>16.6985</v>
       </c>
       <c r="E8" t="n">
-        <v>16.96771</v>
+        <v>16.81092</v>
       </c>
       <c r="F8" t="n">
-        <v>41.85181</v>
+        <v>43.45165</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05147</v>
+        <v>0.0502</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8383</v>
+        <v>1.81353</v>
       </c>
     </row>
     <row r="9">
@@ -638,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.00417</v>
+        <v>16.83221</v>
       </c>
       <c r="D9" t="n">
-        <v>16.96391</v>
+        <v>16.58779</v>
       </c>
       <c r="E9" t="n">
-        <v>16.64478</v>
+        <v>16.83131</v>
       </c>
       <c r="F9" t="n">
-        <v>42.32731</v>
+        <v>42.07722</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05181</v>
+        <v>0.05075</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84877</v>
+        <v>1.79743</v>
       </c>
     </row>
     <row r="10">
@@ -663,31 +660,51 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.74388</v>
+        <v>16.97388</v>
       </c>
       <c r="D10" t="n">
-        <v>16.49059</v>
+        <v>16.77606</v>
       </c>
       <c r="E10" t="n">
-        <v>16.64886</v>
+        <v>16.87493</v>
       </c>
       <c r="F10" t="n">
-        <v>42.86312</v>
+        <v>43.19623</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05138</v>
+        <v>0.05086</v>
       </c>
       <c r="H10" t="n">
-        <v>1.79659</v>
+        <v>1.89086</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -701,14 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>16.96771</v>
       </c>
       <c r="D12" t="n">
-        <v>1.14168</v>
+        <v>16.49846</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.83086</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41.85181</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05147</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.8383</v>
       </c>
     </row>
     <row r="13">
@@ -718,10 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>17.00417</v>
       </c>
       <c r="D13" t="n">
-        <v>1.13381</v>
+        <v>16.64478</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.96391</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.32731</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05181</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.84877</v>
       </c>
     </row>
     <row r="14">
@@ -731,10 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>16.74388</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11335</v>
+        <v>16.49059</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.64886</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.86312</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05138</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.79659</v>
       </c>
     </row>
     <row r="15">
@@ -744,10 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>17.32003</v>
       </c>
       <c r="D15" t="n">
-        <v>1.14026</v>
+        <v>16.87569</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.0214</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.29093</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05018</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.82184</v>
       </c>
     </row>
     <row r="16">
@@ -757,10 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>17.0003</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10639</v>
+        <v>16.41686</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.7937</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.24392</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.82508</v>
       </c>
     </row>
     <row r="17">
@@ -770,10 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>17.18063</v>
       </c>
       <c r="D17" t="n">
-        <v>1.11532</v>
+        <v>16.61423</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.9162</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.61574</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05114</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.82649</v>
       </c>
     </row>
     <row r="18">
@@ -783,10 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>16.67402</v>
       </c>
       <c r="D18" t="n">
-        <v>1.11437</v>
+        <v>16.65209</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.65465</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.68275</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.84397</v>
       </c>
     </row>
     <row r="19">
@@ -796,10 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>16.94302</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11613</v>
+        <v>16.69996</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.87184</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.31467</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05048</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.84941</v>
       </c>
     </row>
     <row r="20">
@@ -809,51 +922,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>17.08919</v>
       </c>
       <c r="D20" t="n">
-        <v>1.11619</v>
+        <v>16.21594</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.86557</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.48607</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05128</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.85001</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -865,32 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7433</v>
+        <v>15.87471</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08123</v>
+        <v>15.17675</v>
       </c>
       <c r="E22" t="n">
-        <v>0.60562</v>
+        <v>15.83454</v>
       </c>
       <c r="F22" t="n">
-        <v>0.96544</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.11045</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.0939</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12729</v>
+        <v>255.98013</v>
       </c>
     </row>
     <row r="23">
@@ -900,28 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.75668</v>
+        <v>16.04868</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0806</v>
+        <v>15.44844</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6057399999999999</v>
+        <v>15.65592</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9760799999999999</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.11118</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00742</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09404</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12645</v>
+        <v>259.59387</v>
       </c>
     </row>
     <row r="24">
@@ -931,28 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75895</v>
+        <v>15.79849</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08222</v>
+        <v>15.23769</v>
       </c>
       <c r="E24" t="n">
-        <v>0.58749</v>
+        <v>15.56628</v>
       </c>
       <c r="F24" t="n">
-        <v>0.97928</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.11069</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09293</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.13027</v>
+        <v>257.58705</v>
       </c>
     </row>
     <row r="25">
@@ -962,28 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.73993</v>
+        <v>15.83686</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08261</v>
+        <v>15.53892</v>
       </c>
       <c r="E25" t="n">
-        <v>0.61155</v>
+        <v>15.58386</v>
       </c>
       <c r="F25" t="n">
-        <v>0.93999</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.10881</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12613</v>
+        <v>254.91579</v>
       </c>
     </row>
     <row r="26">
@@ -993,28 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.74641</v>
+        <v>15.78579</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08112</v>
+        <v>15.41967</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60202</v>
+        <v>15.55221</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9738</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.10779</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09274</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12372</v>
+        <v>257.13158</v>
       </c>
     </row>
     <row r="27">
@@ -1024,28 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7736499999999999</v>
+        <v>16.15248</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08244</v>
+        <v>15.24245</v>
       </c>
       <c r="E27" t="n">
-        <v>0.60527</v>
+        <v>15.6242</v>
       </c>
       <c r="F27" t="n">
-        <v>0.98861</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.11259</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00746</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09292</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12322</v>
+        <v>259.07409</v>
       </c>
     </row>
     <row r="28">
@@ -1055,28 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.74605</v>
+        <v>16.10607</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08108</v>
+        <v>15.63619</v>
       </c>
       <c r="E28" t="n">
-        <v>0.59973</v>
+        <v>16.02583</v>
       </c>
       <c r="F28" t="n">
-        <v>0.94856</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.11156</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09279999999999999</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12704</v>
+        <v>250.03468</v>
       </c>
     </row>
     <row r="29">
@@ -1086,28 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.75117</v>
+        <v>15.65507</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08105999999999999</v>
+        <v>15.18066</v>
       </c>
       <c r="E29" t="n">
-        <v>0.60529</v>
+        <v>15.5763</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9611499999999999</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.11046</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00766</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09338</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12691</v>
+        <v>254.78897</v>
       </c>
     </row>
     <row r="30">
@@ -1117,28 +1126,1070 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.75582</v>
+        <v>15.95863</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08092000000000001</v>
+        <v>15.37673</v>
       </c>
       <c r="E30" t="n">
-        <v>0.60386</v>
+        <v>15.49291</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9709</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.10831</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.007849999999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09297999999999999</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12644</v>
+        <v>259.87733</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.64344</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.05834</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.44445</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.78557</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.09774</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.69373</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.1592</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.54616</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.82197</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.31554</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.85285</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15.98128</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.30413</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.97291</v>
+      </c>
+      <c r="G34" t="n">
+        <v>33.89582</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.26989</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.96856</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.38643</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.67192</v>
+      </c>
+      <c r="G35" t="n">
+        <v>33.3224</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.63397</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.13079</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.48364</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22.26734</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.01575</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.64215</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.22554</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.49428</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.73941</v>
+      </c>
+      <c r="G37" t="n">
+        <v>33.94758</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.80089</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.0701</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.24972</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.89897</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.14859</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.78913</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.23327</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.35049</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.91337</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.58592</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.66592</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.84026</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.59936</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.61715</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.65195</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.76924</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.39124</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.50243</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.59991</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.27148</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.77447</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.08062</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.61299</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.24293</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.5507</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.84429</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.11127</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.61557</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.76421</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.57984</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.85627</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15.99585</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.28389</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.63275</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.57713</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17.1955</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.96129</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.40141</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.85636</v>
+      </c>
+      <c r="G46" t="n">
+        <v>33.38192</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.70428</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.96697</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.50815</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.88139</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.13872</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.91285</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.09104</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.60202</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.06325</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.65364</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.00697</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.68493</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.44722</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.04803</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.44312</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.67733</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.33314</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.46085</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.52334</v>
+      </c>
+      <c r="G50" t="n">
+        <v>33.53391</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.61376</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.11841</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.61044</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.10225</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.61681</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.12762</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.61233</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.10578</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.61956</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.13271</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.60378</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.10861</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6009100000000001</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.13841</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.61233</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.13445</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.61167</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.12074</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.62003</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.11959</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.60533</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.10578</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.61944</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.10438</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.60875</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.13117</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.6157</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.12904</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.6061299999999999</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.11968</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.61527</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.14462</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.61451</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.12278</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.6061299999999999</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.12235</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.75791</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.98519</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.11075</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09365</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12962</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.7571600000000001</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08144999999999999</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.61858</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.97219</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.10838</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09376</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12811</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.75557</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08128000000000001</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.61283</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.96055</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.10938</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09433</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12948</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.75467</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08223</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.60623</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.96152</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.10935</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09514</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.1285</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.74729</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08184</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.60794</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.96285</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.11007</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09472</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12789</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.76489</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.0823</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.63512</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.95491</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.10845</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09379</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12613</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.75038</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08122</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.60963</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.96567</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.11007</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09354</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12628</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.75688</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08123</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.60367</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.9552</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.10883</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00742</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09332</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12576</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.74981</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08125</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.10962</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09372</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12765</v>
       </c>
     </row>
   </sheetData>
